--- a/data/extracted/inventory-receipts/REP CONTENEDOR P310 26F.XLSX
+++ b/data/extracted/inventory-receipts/REP CONTENEDOR P310 26F.XLSX
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69C4824-1F77-4157-8DFF-B3118C49CE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -680,7 +693,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -721,12 +734,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1006,50 +1018,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L126"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1087,12 +1099,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1130,7 +1142,7 @@
         <v>19.149999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1168,7 +1180,7 @@
         <v>18.98</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1206,7 +1218,7 @@
         <v>19.239999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1244,7 +1256,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1282,7 +1294,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1320,7 +1332,7 @@
         <v>19.32</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1358,7 +1370,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1396,7 +1408,7 @@
         <v>19.62</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,7 +1446,7 @@
         <v>19.190000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F16" s="1" t="s">
         <v>45</v>
       </c>
@@ -1454,7 +1466,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F17" s="1" t="s">
         <v>43</v>
       </c>
@@ -1477,7 +1489,7 @@
         <v>169.81</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1515,7 +1527,7 @@
         <v>19.010000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1553,7 +1565,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1591,7 +1603,7 @@
         <v>19.079999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1629,7 +1641,7 @@
         <v>18.89</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1667,7 +1679,7 @@
         <v>18.739999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -1705,7 +1717,7 @@
         <v>17.649999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1743,7 +1755,7 @@
         <v>18.91</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1781,7 +1793,7 @@
         <v>19.05</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -1819,7 +1831,7 @@
         <v>18.12</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F27" s="1" t="s">
         <v>45</v>
       </c>
@@ -1839,7 +1851,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F28" s="1" t="s">
         <v>59</v>
       </c>
@@ -1859,7 +1871,7 @@
         <v>168.15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -1897,7 +1909,7 @@
         <v>17.89</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -1935,7 +1947,7 @@
         <v>15.87</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -1973,7 +1985,7 @@
         <v>17.649999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -2011,7 +2023,7 @@
         <v>17.670000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -2049,7 +2061,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,7 +2099,7 @@
         <v>17.46</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -2125,7 +2137,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -2163,7 +2175,7 @@
         <v>17.28</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -2201,7 +2213,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -2239,7 +2251,7 @@
         <v>17.489999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -2277,7 +2289,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -2315,7 +2327,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -2353,7 +2365,7 @@
         <v>14.01</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -2391,7 +2403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -2429,7 +2441,7 @@
         <v>18.809999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -2467,7 +2479,7 @@
         <v>17.36</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -2505,7 +2517,7 @@
         <v>19.03</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -2543,7 +2555,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -2581,7 +2593,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -2619,7 +2631,7 @@
         <v>17.489999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -2657,7 +2669,7 @@
         <v>15.83</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -2695,7 +2707,7 @@
         <v>17.91</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -2733,7 +2745,7 @@
         <v>17.940000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -2771,7 +2783,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -2809,7 +2821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -2847,7 +2859,7 @@
         <v>17.79</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -2885,7 +2897,7 @@
         <v>17.850000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -2923,7 +2935,7 @@
         <v>18.14</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -2961,7 +2973,7 @@
         <v>17.829999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -2999,7 +3011,7 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -3037,7 +3049,7 @@
         <v>17.940000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -3075,7 +3087,7 @@
         <v>17.84</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -3113,7 +3125,7 @@
         <v>18.010000000000002</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -3151,7 +3163,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -3189,7 +3201,7 @@
         <v>14.64</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3227,7 +3239,7 @@
         <v>18.02</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -3265,7 +3277,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -3303,7 +3315,7 @@
         <v>18.18</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -3341,7 +3353,7 @@
         <v>17.82</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -3379,7 +3391,7 @@
         <v>18.29</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -3417,7 +3429,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -3455,7 +3467,7 @@
         <v>17.760000000000002</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -3493,7 +3505,7 @@
         <v>17.920000000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -3531,7 +3543,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -3569,7 +3581,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -3607,7 +3619,7 @@
         <v>17.36</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -3645,7 +3657,7 @@
         <v>17.239999999999998</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -3683,7 +3695,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -3721,7 +3733,7 @@
         <v>17.63</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -3759,7 +3771,7 @@
         <v>17.03</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -3797,7 +3809,7 @@
         <v>17.329999999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -3835,7 +3847,7 @@
         <v>17.71</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -3873,7 +3885,7 @@
         <v>17.59</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -3911,7 +3923,7 @@
         <v>17.54</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -3949,7 +3961,7 @@
         <v>17.53</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -3987,7 +3999,7 @@
         <v>17.41</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -4025,7 +4037,7 @@
         <v>17.690000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -4063,7 +4075,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -4101,7 +4113,7 @@
         <v>18.09</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -4139,7 +4151,7 @@
         <v>17.97</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -4177,7 +4189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -4215,7 +4227,7 @@
         <v>18.09</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -4253,7 +4265,7 @@
         <v>17.87</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -4291,7 +4303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -4329,7 +4341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -4367,7 +4379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -4405,7 +4417,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -4443,7 +4455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -4481,7 +4493,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -4519,7 +4531,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -4557,7 +4569,7 @@
         <v>17.41</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -4595,7 +4607,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -4633,7 +4645,7 @@
         <v>17.579999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F102" s="1" t="s">
         <v>45</v>
       </c>
@@ -4653,7 +4665,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F103" s="1" t="s">
         <v>196</v>
       </c>
@@ -4673,7 +4685,7 @@
         <v>1279.55</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -4711,7 +4723,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -4749,7 +4761,7 @@
         <v>20.03</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -4787,7 +4799,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -4825,7 +4837,7 @@
         <v>20.71</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -4863,7 +4875,7 @@
         <v>18.82</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -4901,7 +4913,7 @@
         <v>19.579999999999998</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -4939,7 +4951,7 @@
         <v>20.059999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -4977,7 +4989,7 @@
         <v>20.12</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -5015,7 +5027,7 @@
         <v>21.09</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F113" s="1" t="s">
         <v>45</v>
       </c>
@@ -5035,7 +5047,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F114" s="1" t="s">
         <v>43</v>
       </c>
@@ -5058,7 +5070,7 @@
         <v>178.89</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F115" s="1" t="s">
         <v>45</v>
       </c>
@@ -5078,7 +5090,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>210</v>
       </c>
@@ -5116,7 +5128,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F117" s="1" t="s">
         <v>45</v>
       </c>
@@ -5136,7 +5148,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>210</v>
       </c>
@@ -5174,7 +5186,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F120" s="1" t="s">
         <v>45</v>
       </c>
@@ -5194,12 +5206,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K121" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>210</v>
       </c>
@@ -5237,7 +5249,7 @@
         <v>71.349999999999994</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F123" s="1" t="s">
         <v>45</v>
       </c>
@@ -5257,12 +5269,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K124" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>210</v>
       </c>
@@ -5300,7 +5312,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F126" s="1" t="s">
         <v>45</v>
       </c>
@@ -5324,4 +5336,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E0F201-0608-4050-92DC-B288376D78FB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>